--- a/output/pdf_financials_xlsx/MVMD.xlsx
+++ b/output/pdf_financials_xlsx/MVMD.xlsx
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>7.67</v>
+        <v>-7.67</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7.472</v>
+        <v>-7.472</v>
       </c>
     </row>
     <row r="17">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>7.67</v>
+        <v>-7.67</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>7.472</v>
+        <v>-7.472</v>
       </c>
     </row>
     <row r="21">
@@ -834,10 +834,10 @@
         <v>-7.442</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>7.67</v>
+        <v>-7.67</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>7.472</v>
+        <v>-7.472</v>
       </c>
     </row>
     <row r="24">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-383.5</v>
+        <v>383.5</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-373.6</v>
+        <v>373.6</v>
       </c>
     </row>
     <row r="27">
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7.67</v>
+        <v>-7.67</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>7.472</v>
+        <v>-7.472</v>
       </c>
     </row>
     <row r="28">
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.934</v>
+        <v>-7.406</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7.577</v>
+        <v>-7.367</v>
       </c>
     </row>
     <row r="30">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>13223.33333333333</v>
+        <v>-12343.33333333333</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>15463.26530612245</v>
+        <v>-15034.69387755102</v>
       </c>
     </row>
     <row r="31">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>12783.33333333333</v>
+        <v>-12783.33333333333</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>15248.97959183673</v>
+        <v>-15248.97959183673</v>
       </c>
     </row>
     <row r="33">
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>7.67</v>
+        <v>-7.67</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>7.472</v>
+        <v>-7.472</v>
       </c>
     </row>
     <row r="103">
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>7.442</v>
+        <v>-7.442</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MVMD.xlsx
+++ b/output/pdf_financials_xlsx/MVMD.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.274</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="13">
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.67</v>
+        <v>-7.396</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.472</v>
+        <v>-7.364</v>
       </c>
     </row>
     <row r="28">
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.406</v>
+        <v>-7.132</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.367</v>
+        <v>-7.259</v>
       </c>
     </row>
     <row r="30">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-12343.33333333333</v>
+        <v>-11886.66666666667</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-15034.69387755102</v>
+        <v>-14814.28571428571</v>
       </c>
     </row>
     <row r="31">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">

--- a/output/pdf_financials_xlsx/MVMD.xlsx
+++ b/output/pdf_financials_xlsx/MVMD.xlsx
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.264</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="101">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">

--- a/output/pdf_financials_xlsx/MVMD.xlsx
+++ b/output/pdf_financials_xlsx/MVMD.xlsx
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-7.67</v>
+        <v>-7.762</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-7.472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>0.092</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.472</v>
       </c>
     </row>
     <row r="18">
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.396</v>
+        <v>-7.488</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.364</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="28">
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.132</v>
+        <v>-7.224</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.259</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="30">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-11886.66666666667</v>
+        <v>-12040</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-14814.28571428571</v>
+        <v>434.6938775510204</v>
       </c>
     </row>
     <row r="31">
@@ -978,10 +978,12 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.185261530533368</v>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2101,13 +2103,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="102">
@@ -2181,13 +2183,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-1.842</v>
+        <v>-1.807</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.287</v>
+        <v>-0.274</v>
       </c>
     </row>
     <row r="107">
@@ -2341,10 +2343,10 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -4476,7 +4478,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>-0.008</v>
       </c>
@@ -4718,7 +4724,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>-0.064</v>
       </c>
@@ -5799,7 +5809,11 @@
           <t>Net loss and comprehensive loss for the year before income tax recovery</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -5828,7 +5842,11 @@
           <t>Income tax (recovery) expense 17</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -6319,7 +6337,11 @@
           <t>Net loss and comprehensive loss for the year before income tax recovery 7,762</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -6350,7 +6372,11 @@
           <t>Income tax (recovery) expense 17 (92)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
